--- a/supplementary-materials/ビットカウント.xlsx
+++ b/supplementary-materials/ビットカウント.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ict15\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ict15\Desktop\資料集\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8556C57D-0EC5-468A-8AFE-7327754B99B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9A53FD-DF10-480B-A1DB-B3D593D8AE63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="825" yWindow="225" windowWidth="26955" windowHeight="13920" activeTab="6" xr2:uid="{6F445B1B-4C61-41ED-9A1E-C5DBD9F9D530}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{6F445B1B-4C61-41ED-9A1E-C5DBD9F9D530}"/>
   </bookViews>
   <sheets>
     <sheet name="はじめに" sheetId="1" r:id="rId1"/>
@@ -20,9 +20,10 @@
     <sheet name="方法4" sheetId="6" r:id="rId5"/>
     <sheet name="方法5" sheetId="7" r:id="rId6"/>
     <sheet name="まとめ" sheetId="2" r:id="rId7"/>
-    <sheet name="発展" sheetId="9" r:id="rId8"/>
-    <sheet name="AIの解答" sheetId="10" r:id="rId9"/>
-    <sheet name="おまけ" sheetId="3" r:id="rId10"/>
+    <sheet name="最適化の考察" sheetId="11" r:id="rId8"/>
+    <sheet name="発展" sheetId="9" r:id="rId9"/>
+    <sheet name="AIの解答" sheetId="10" r:id="rId10"/>
+    <sheet name="おまけ" sheetId="3" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="266">
   <si>
     <t>関数名</t>
   </si>
@@ -80,24 +81,12 @@
     <t>numofbits3 (カーニハン流)</t>
   </si>
   <si>
-    <t>約1.6倍速</t>
-  </si>
-  <si>
     <t>ビットが「0」ばかりのスカスカなデータ（疎な行列）のときに圧倒的な効果を発揮。</t>
   </si>
   <si>
-    <t>約11.0倍速</t>
-  </si>
-  <si>
-    <t>約16.0倍速</t>
-  </si>
-  <si>
     <t>numofbits2 (空間置換テーブル)</t>
   </si>
   <si>
-    <t>約42.0倍速</t>
-  </si>
-  <si>
     <t>計算のプリコンパイル（空間への置換）。256配列のテーブルをメモリ展開。</t>
   </si>
   <si>
@@ -105,9 +94,6 @@
   </si>
   <si>
     <t>popcnt (CPUダイレクト)</t>
-  </si>
-  <si>
-    <t>約80.0倍速</t>
   </si>
   <si>
     <t>ハードウェア層へのダイレクトコミット。CPUが持つ専用の物理回路を直接叩く。</t>
@@ -1092,10 +1078,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>以下は、同一環境（CPU）において、各ビットカウント・アルゴリズムを「100回」回した際の物理的な処理時間のログデータです。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>また専用回路がある場合のpopcnt関数を利用した方法でも測定しています。</t>
     <rPh sb="2" eb="4">
       <t>センヨウ</t>
@@ -1489,14 +1471,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>最速と最遅で、なんと「約80倍」の処理速度差になります。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>【まとめ】AI時代を生き抜く、アーキテクトの心構え</t>
-  </si>
-  <si>
-    <t>• 「どれが良いとか、悪いとかはない。状況により、最適なものを選べることが大事」</t>
   </si>
   <si>
     <t>さまざまなケース（制約条件）に応じて、引き出し（別解）の中から</t>
@@ -2907,12 +2882,610 @@
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>以下は、同一環境（CPU）において、各ビットカウント・アルゴリズムを「1億回」回した際の物理的な処理時間のログデータです。</t>
+    <rPh sb="36" eb="37">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>約21.0倍速</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>約30.0倍速</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>約13.8倍速</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>約3.75倍速</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>最速と最遅で、なんと「約30倍」の処理速度差になります。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Cでの最適化、javaとの比較</t>
+    <rPh sb="3" eb="6">
+      <t>サイテキカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒカク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>以下は、同一環境（CPU）において、Cの最適化オプションを追加した場合いと、同様のコードをjavaで処理したときの比較一覧です</t>
+    <rPh sb="20" eb="23">
+      <t>サイテキカ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ドウヨウ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ヒカク</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>処理時間比較一覧：処理時間（秒）</t>
+    <rPh sb="4" eb="6">
+      <t>ヒカク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>C：最適化なし</t>
+    <rPh sb="2" eb="5">
+      <t>サイテキカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>C：最適化あり</t>
+    <rPh sb="2" eb="5">
+      <t>サイテキカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>5.366倍</t>
+    <rPh sb="5" eb="6">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>7.413倍</t>
+    <rPh sb="5" eb="6">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>34.370倍</t>
+    <rPh sb="6" eb="7">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2.268倍</t>
+    <rPh sb="5" eb="6">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2.356倍</t>
+    <rPh sb="5" eb="6">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>4.347倍</t>
+    <rPh sb="5" eb="6">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>volatile修飾</t>
+    <rPh sb="8" eb="10">
+      <t>シュウショク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>volatile時の効率</t>
+    <rPh sb="8" eb="9">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウリツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Cの最適化ありなしでは全て処理時間が短くなることが分かる。</t>
+    <rPh sb="2" eb="4">
+      <t>サイテキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ミジカ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>numofbits3 (カーニハン流)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>最適化による処理は、処理自体も変更される場合があるそうなので、</t>
+    <rPh sb="0" eb="3">
+      <t>サイテキカ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジタイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>処理時間が短くなるのは当然としても、numofbits3の伸びが他に比べて顕著になった。</t>
+    <rPh sb="29" eb="30">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>クラ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ケンチョ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>比較のためにnumofbits3については、volatile修飾により処理内容は変えない場合の比較も行った。</t>
+    <rPh sb="0" eb="2">
+      <t>ヒカク</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>シュウショク</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ヒカク</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2.7242倍</t>
+    <rPh sb="6" eb="7">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>numofbits1 (力まかせループ)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>組込み命令のpopcntとほぼ同じ処理速度になるのは、処理内容からしても異常な伸びである。</t>
+    <rPh sb="0" eb="2">
+      <t>クミコ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>メイレイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ノ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは最適化処理により、内部的にpopcnt命令に置換わっていると推測される。</t>
+    <rPh sb="3" eb="6">
+      <t>サイテキカ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ナイブ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>メイレイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>オキカ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>スイソク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>最適化により、実際の処理自体が変更されるという前提で、javaでの結果を見ると</t>
+    <rPh sb="0" eb="3">
+      <t>サイテキカ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジタイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ゼンテイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>C：最適化効率</t>
+    <rPh sb="2" eb="5">
+      <t>サイテキカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウリツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>この場合はループ回数が平均でnumofbits1 の半分になることから、numofbits1の半分程度の時間となり予測通りの値に収まる。</t>
+    <rPh sb="2" eb="4">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カイスウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヘイキン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ハンブン</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ハンブン</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>テイド</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ヨソク</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>ドオ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="64" eb="65">
+      <t>オサ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>c：vscodeベースでgccを組み込んでの実施</t>
+    <rPh sb="16" eb="17">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ジッシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>java：IntelliJ IDEA</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>javaデフォルト</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>java（-Xint）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>こちらも検証として、VMの最適化を行わないオプション-Xintで計測してみた。</t>
+    <rPh sb="4" eb="6">
+      <t>ケンショウ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>サイテキカ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ケイソク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2、4、5が組込み命令と同じ速度になるのは、内部でpopcnt命令として処理されていることが推測できる。</t>
+    <rPh sb="6" eb="8">
+      <t>クミコ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>メイレイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ナイブ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>メイレイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>スイソク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>やはり予測通り最適化を行わないと、2、4、5と組込み命令、それぞれ異なる傾向となった。</t>
+    <rPh sb="3" eb="5">
+      <t>ヨソク</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ドオ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>サイテキカ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ケイコウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>また興味深い結果として、組込み関数popcntよりnumofbits4 (HAKMEMの魔術)が最速となったことである。</t>
+    <rPh sb="2" eb="5">
+      <t>キョウミブカ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>クミコ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カンスウ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>サイソク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは中間コードからのpopcnt命令呼び出しと、コード自体が軽量なHAKMEMの魔術の比較で、</t>
+    <rPh sb="3" eb="5">
+      <t>チュウカン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>メイレイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ジタイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ケイリョウ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ヒカク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>呼び出しがオーバーヘッドとなり、僅かだが速度が逆転したことが見て取れる。</t>
+    <rPh sb="0" eb="1">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ワズ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ギャクテン</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>【考察】コンパイル時の最適化</t>
+    <rPh sb="1" eb="3">
+      <t>コウサツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>サイテキカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>• 「どれが良いとか、悪いとかはない。状況により、最適なものを選べることが大事」</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「まとめ」シートで触れた内容ではあるが、こちらの検証でも、環境、状況により最適なコードは変化する。</t>
+    <rPh sb="9" eb="10">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ケンショウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>サイテキ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ヘンカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「どれが良いとか、悪いとかはない。状況により、最適なものを選べることが大事」を裏付ける結果となった。</t>
+    <rPh sb="39" eb="41">
+      <t>ウラヅ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3040,8 +3613,23 @@
       <name val="Segoe UI Symbol"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3051,6 +3639,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3121,7 +3715,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3167,16 +3761,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -8058,99 +8673,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AD7EDBF-D96A-4EEC-80E9-08D2FFECC2D7}">
   <dimension ref="A2:A22"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:1">
       <c r="A2" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" s="3"/>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:1">
       <c r="A4" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:1">
       <c r="A6" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="3"/>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="3"/>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="3"/>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+    <row r="17" spans="1:1">
+      <c r="A17" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A8" s="3" t="s">
+    <row r="18" spans="1:1">
+      <c r="A18" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A9" s="3"/>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A10" s="3" t="s">
+    <row r="19" spans="1:1">
+      <c r="A19" s="3"/>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A11" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A12" s="3"/>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A13" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A14" s="3" t="s">
+    <row r="21" spans="1:1">
+      <c r="A21" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A15" s="3"/>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A16" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A17" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A18" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A19" s="3"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A20" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A21" s="3" t="s">
+    <row r="22" spans="1:1">
+      <c r="A22" s="3" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A22" s="3" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -8160,170 +8775,320 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A96CF2DE-57FC-4DB4-A84A-A9E649FFD8DD}">
+  <dimension ref="A1:P55"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" t="s">
+        <v>129</v>
+      </c>
+      <c r="P40" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41" t="s">
+        <v>219</v>
+      </c>
+      <c r="P41" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42" t="s">
+        <v>125</v>
+      </c>
+      <c r="P42" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" t="s">
+        <v>131</v>
+      </c>
+      <c r="P43" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="P44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" t="s">
+        <v>217</v>
+      </c>
+      <c r="P45" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" t="s">
+        <v>130</v>
+      </c>
+      <c r="P46" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" t="s">
+        <v>127</v>
+      </c>
+      <c r="P47" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>133</v>
+      </c>
+      <c r="C52" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>134</v>
+      </c>
+      <c r="C53" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>135</v>
+      </c>
+      <c r="C54" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>136</v>
+      </c>
+      <c r="C55" t="s">
+        <v>216</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3162D090-449F-4521-9405-36EE3D39945F}">
   <dimension ref="A2:A36"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:1">
       <c r="A2" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="4"/>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="3"/>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A3" s="6" t="s">
+    <row r="15" spans="1:1">
+      <c r="A15" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="3"/>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A4" s="4"/>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A6" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+    <row r="31" spans="1:1">
+      <c r="A31" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A8" s="3" t="s">
+    <row r="33" spans="1:1">
+      <c r="A33" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A9" s="3" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A10" s="3"/>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A11" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A12" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A13" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A14" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A15" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A16" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A17" s="3" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A18" s="3" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A19" s="3" t="s">
+    <row r="34" spans="1:1">
+      <c r="A34" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="7" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A20" s="3"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A21" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A22" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A23" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A24" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A25" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A26" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A27" s="4" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A29" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A30" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A31" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A32" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A33" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A34" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A35" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:1">
       <c r="A36" s="3"/>
     </row>
   </sheetData>
@@ -8335,37 +9100,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35895A5F-7663-4B09-B16B-0AC47B118855}">
   <dimension ref="A3:F15"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6">
       <c r="A3" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="F5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="19.5" x14ac:dyDescent="0.4">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="19.5">
       <c r="F6" s="10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="F7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="F8" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="9"/>
     </row>
   </sheetData>
@@ -8378,46 +9143,46 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFCE23BD-CC9A-4C68-AC94-0A739197F41E}">
   <dimension ref="A3:J10"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10">
       <c r="A3" s="11" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="J4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="J5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="J6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="J7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="J8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="J9" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="J10" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -8430,44 +9195,44 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A35231-C07A-43D8-B1B7-F0C678E17E5E}">
   <dimension ref="A3:F10"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6">
       <c r="A3" s="8" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="F4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="F5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="F6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="F8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="F9" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="F8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="F9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6">
       <c r="F10" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -8480,156 +9245,156 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06FC88A2-72EB-4DD1-9F80-787E4169999C}">
   <dimension ref="A3:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16">
       <c r="A3" s="12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="I4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="I5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="I6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="I7" t="s">
+        <v>80</v>
+      </c>
+      <c r="O7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="I4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="I5" t="s">
+    <row r="8" spans="1:16">
+      <c r="I8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="I9" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="I6" t="s">
+    <row r="10" spans="1:16">
+      <c r="I10" t="s">
+        <v>90</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="I7" t="s">
+      <c r="L10" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="O7" t="s">
+      <c r="M10" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="N10" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="I8" t="s">
+      <c r="O10" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="P10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="I11" t="s">
+        <v>92</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="N11" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="I9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="I10" t="s">
+      <c r="O11" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="P11" s="14" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="19.5" thickBot="1">
+      <c r="I12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="19.5" thickBot="1">
+      <c r="J13" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="K13" s="18"/>
+      <c r="L13" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="M13" s="18"/>
+      <c r="N13" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="P10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="I11" t="s">
+      <c r="O13" s="18"/>
+      <c r="P13" t="s">
         <v>98</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="P11" s="14" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="I12" t="s">
+    </row>
+    <row r="14" spans="1:16">
+      <c r="I14" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="J13" s="15" t="s">
+    <row r="15" spans="1:16">
+      <c r="B15" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="I15" t="s">
         <v>100</v>
       </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="15" t="s">
+    </row>
+    <row r="16" spans="1:16">
+      <c r="I16" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" spans="9:9">
+      <c r="I17" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="18" spans="9:9">
+      <c r="I18" t="s">
         <v>101</v>
       </c>
-      <c r="M13" s="16"/>
-      <c r="N13" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="O13" s="16"/>
-      <c r="P13" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="I14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="B15" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="I15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="I16" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="17" spans="9:9" x14ac:dyDescent="0.4">
-      <c r="I17" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="18" spans="9:9" x14ac:dyDescent="0.4">
-      <c r="I18" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="19" spans="9:9" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="9:9">
       <c r="I19" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="20" spans="9:9" x14ac:dyDescent="0.4">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="20" spans="9:9">
       <c r="I20" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -8647,56 +9412,56 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC68B9E7-1246-4F8F-8D8C-50EB9F5D9333}">
   <dimension ref="A3:H13"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8">
       <c r="A3" s="8" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="H4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="H5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="H6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="H7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="H8" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="H9" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="H11" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="H12" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="H13" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -8709,7 +9474,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1E298B5-2B38-4D99-9BE4-F5915ADA9AFC}">
   <dimension ref="B2:F31"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="30.25" bestFit="1" customWidth="1"/>
@@ -8719,27 +9484,27 @@
     <col min="6" max="6" width="87.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6">
       <c r="B2" s="12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6">
+      <c r="B3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6">
+      <c r="B4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6">
       <c r="B5" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.4">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6">
       <c r="B7" s="2" t="s">
         <v>0</v>
       </c>
@@ -8756,12 +9521,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="1">
-        <v>27.376000000000001</v>
+        <v>9.4060000000000006</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>6</v>
@@ -8773,164 +9538,164 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6">
       <c r="B9" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C9" s="1">
-        <v>0.65700000000000003</v>
+        <v>0.68200000000000005</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>15</v>
+        <v>223</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6">
       <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="1">
-        <v>16.754999999999999</v>
+        <v>2.5089999999999999</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="2:6">
       <c r="B11" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C11" s="1">
-        <v>2.4340000000000002</v>
+        <v>0.44900000000000001</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>12</v>
+        <v>221</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6">
       <c r="B12" s="1" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C12" s="1">
-        <v>1.6779999999999999</v>
+        <v>0.45</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>13</v>
+        <v>221</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6">
       <c r="B13" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C13" s="1">
-        <v>0.33800000000000002</v>
+        <v>0.313</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>19</v>
+        <v>222</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6">
       <c r="B15" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="12" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" s="12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B17" s="12" t="s">
+    <row r="30" spans="2:2">
+      <c r="B30" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" t="s">
         <v>118</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B18" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B19" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B20" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B21" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B23" s="12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B24" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B25" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B26" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B27" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B28" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B29" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B30" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B31" t="s">
-        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -8940,452 +9705,609 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF289246-A155-4A1B-856A-95F9E049863F}">
-  <dimension ref="A1:Q41"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC76AE33-ADCE-498E-B3F4-16DB3E394204}">
+  <dimension ref="B2:I32"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="4.5" customWidth="1"/>
+    <col min="2" max="2" width="30.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A1" s="18" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A2" s="12" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A9" s="17" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
-        <v>169</v>
-      </c>
-      <c r="M23" t="s">
-        <v>183</v>
-      </c>
-      <c r="N23" t="s">
-        <v>180</v>
-      </c>
-      <c r="O23" t="s">
-        <v>181</v>
-      </c>
-      <c r="P23" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
-        <v>170</v>
-      </c>
-      <c r="M24">
-        <v>1</v>
-      </c>
-      <c r="N24">
-        <f>M24*10</f>
-        <v>10</v>
-      </c>
-      <c r="O24">
-        <f>M24*2</f>
-        <v>2</v>
-      </c>
-      <c r="P24">
-        <f>M24</f>
-        <v>1</v>
-      </c>
-      <c r="Q24">
-        <f>20*LOG(M24)+10</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
-        <v>171</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="M25">
-        <v>10</v>
-      </c>
-      <c r="N25">
-        <f t="shared" ref="N25:N28" si="0">M25*10</f>
-        <v>100</v>
-      </c>
-      <c r="O25">
-        <f t="shared" ref="O25:O28" si="1">M25*2</f>
-        <v>20</v>
-      </c>
-      <c r="P25">
-        <f t="shared" ref="P25:P28" si="2">M25</f>
-        <v>10</v>
-      </c>
-      <c r="Q25">
-        <f t="shared" ref="Q25:Q28" si="3">20*LOG(M25)+10</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
-        <v>176</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="M26">
-        <v>100</v>
-      </c>
-      <c r="N26">
-        <f t="shared" si="0"/>
-        <v>1000</v>
-      </c>
-      <c r="O26">
-        <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="P26">
-        <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="Q26">
-        <f t="shared" si="3"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
-        <v>172</v>
-      </c>
-      <c r="D27" t="s">
-        <v>216</v>
-      </c>
-      <c r="M27">
-        <v>1000</v>
-      </c>
-      <c r="N27">
-        <f t="shared" si="0"/>
-        <v>10000</v>
-      </c>
-      <c r="O27">
-        <f t="shared" si="1"/>
-        <v>2000</v>
-      </c>
-      <c r="P27">
-        <f t="shared" si="2"/>
-        <v>1000</v>
-      </c>
-      <c r="Q27">
-        <f t="shared" si="3"/>
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
-        <v>173</v>
-      </c>
-      <c r="M28">
-        <v>10000</v>
-      </c>
-      <c r="N28">
-        <f t="shared" si="0"/>
-        <v>100000</v>
-      </c>
-      <c r="O28">
-        <f t="shared" si="1"/>
-        <v>20000</v>
-      </c>
-      <c r="P28">
-        <f t="shared" si="2"/>
-        <v>10000</v>
-      </c>
-      <c r="Q28">
-        <f t="shared" si="3"/>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A29" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A30" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A31" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A32" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A33" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A34" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A36" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A37" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A38" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A39" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A40" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A41" t="s">
-        <v>191</v>
+    <row r="2" spans="2:9">
+      <c r="B2" s="12" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9">
+      <c r="B3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9">
+      <c r="B4" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9">
+      <c r="B5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9">
+      <c r="B7" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9">
+      <c r="B8" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C8" s="1">
+        <v>9.4060000000000006</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1.7529999999999999</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="H8" s="24">
+        <v>21.920999999999999</v>
+      </c>
+      <c r="I8" s="24">
+        <v>39.664000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9">
+      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.68200000000000005</v>
+      </c>
+      <c r="D9" s="1">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="H9" s="25">
+        <v>8.7050000000000001</v>
+      </c>
+      <c r="I9" s="25">
+        <v>17.035</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9">
+      <c r="B10" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.5089999999999999</v>
+      </c>
+      <c r="D10" s="21">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="F10" s="20">
+        <v>0.92100000000000004</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="H10" s="25">
+        <v>13.923999999999999</v>
+      </c>
+      <c r="I10" s="25">
+        <v>22.550999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9">
+      <c r="B11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.44900000000000001</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="H11" s="25">
+        <v>8.6920000000000002</v>
+      </c>
+      <c r="I11" s="25">
+        <v>13.584</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9">
+      <c r="B12" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.191</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="H12" s="25">
+        <v>8.7040000000000006</v>
+      </c>
+      <c r="I12" s="25">
+        <v>15.981</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9">
+      <c r="B13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.313</v>
+      </c>
+      <c r="D13" s="1">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="H13" s="25">
+        <v>8.6910000000000007</v>
+      </c>
+      <c r="I13" s="25">
+        <v>16.173999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9">
+      <c r="B15" s="12" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9">
+      <c r="B16" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="15" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="23" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="23" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="23" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="23" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" s="23" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" s="23" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="23" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" s="15" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="15" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" s="15" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="15" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="15" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" t="s">
+        <v>265</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A96CF2DE-57FC-4DB4-A84A-A9E649FFD8DD}">
-  <dimension ref="A1:P55"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF289246-A155-4A1B-856A-95F9E049863F}">
+  <dimension ref="A1:Q41"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1">
+      <c r="A1" s="16" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="12" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.4">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
+      <c r="A18" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
+      <c r="A22" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23" t="s">
+        <v>161</v>
+      </c>
+      <c r="M23" t="s">
+        <v>175</v>
+      </c>
+      <c r="N23" t="s">
+        <v>172</v>
+      </c>
+      <c r="O23" t="s">
+        <v>173</v>
+      </c>
+      <c r="P23" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
+      <c r="A24" t="s">
+        <v>162</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <f>M24*10</f>
+        <v>10</v>
+      </c>
+      <c r="O24">
+        <f>M24*2</f>
+        <v>2</v>
+      </c>
+      <c r="P24">
+        <f>M24</f>
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <f>20*LOG(M24)+10</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" t="s">
+        <v>163</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="M25">
+        <v>10</v>
+      </c>
+      <c r="N25">
+        <f t="shared" ref="N25:N28" si="0">M25*10</f>
+        <v>100</v>
+      </c>
+      <c r="O25">
+        <f t="shared" ref="O25:O28" si="1">M25*2</f>
+        <v>20</v>
+      </c>
+      <c r="P25">
+        <f t="shared" ref="P25:P28" si="2">M25</f>
+        <v>10</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" ref="Q25:Q28" si="3">20*LOG(M25)+10</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26" t="s">
+        <v>168</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="M26">
+        <v>100</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="P26">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" t="s">
+        <v>164</v>
+      </c>
+      <c r="D27" t="s">
+        <v>208</v>
+      </c>
+      <c r="M27">
+        <v>1000</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="0"/>
+        <v>10000</v>
+      </c>
+      <c r="O27">
+        <f t="shared" si="1"/>
+        <v>2000</v>
+      </c>
+      <c r="P27">
+        <f t="shared" si="2"/>
+        <v>1000</v>
+      </c>
+      <c r="Q27">
+        <f t="shared" si="3"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28" t="s">
+        <v>165</v>
+      </c>
+      <c r="M28">
+        <v>10000</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="0"/>
+        <v>100000</v>
+      </c>
+      <c r="O28">
+        <f t="shared" si="1"/>
+        <v>20000</v>
+      </c>
+      <c r="P28">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="Q28">
+        <f t="shared" si="3"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17">
+      <c r="A29" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17">
+      <c r="A30" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17">
+      <c r="A31" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17">
+      <c r="A32" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>137</v>
-      </c>
-      <c r="P40" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.4">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>227</v>
-      </c>
-      <c r="P41" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A42" t="s">
-        <v>133</v>
-      </c>
-      <c r="P42" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A43" t="s">
-        <v>139</v>
-      </c>
-      <c r="P43" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="P44" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A45" t="s">
-        <v>225</v>
-      </c>
-      <c r="P45" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A46" t="s">
-        <v>138</v>
-      </c>
-      <c r="P46" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A47" t="s">
-        <v>135</v>
-      </c>
-      <c r="P47" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A48" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A49" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A51" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A52" t="s">
-        <v>141</v>
-      </c>
-      <c r="C52" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A53" t="s">
-        <v>142</v>
-      </c>
-      <c r="C53" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A54" t="s">
-        <v>143</v>
-      </c>
-      <c r="C54" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A55" t="s">
-        <v>144</v>
-      </c>
-      <c r="C55" t="s">
-        <v>224</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
